--- a/tests/第二轮测试用例数据清单.xlsx
+++ b/tests/第二轮测试用例数据清单.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实例总览" sheetId="1" r:id="R60c7c3e588a64ab0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="请求与文件数据" sheetId="2" r:id="R9c7e9f6b0b8f491b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实例总览" sheetId="1" r:id="Rd1d8dc1195084fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="请求与文件数据" sheetId="2" r:id="R37f8b053bc2e4adf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -79,7 +79,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="12">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -104,6 +104,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -308,7 +311,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="15" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="48" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="92" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="62" hidden="0" customWidth="1"/>
@@ -341,12 +344,17 @@
         <x:v>文件目录</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="44" customHeight="1">
+    <x:row r="5" ht="96" hidden="0" customHeight="1">
       <x:c r="A5" s="5" t="str">
         <x:v>R201-01</x:v>
       </x:c>
-      <x:c r="B5" s="5" t="str">
-        <x:v>正常修改并保留排位</x:v>
+      <x:c r="B5" s="11" t="str">
+        <x:v>【场景】在售期间修改等待买家的联系信息
+【前置数据】卖家以 admin / 123456 登录，创建“商品”，价格88.50元。先提交“队首”/13800000001，再提交“等待买家”/13800000002，后者排第2位。
+【测试输入】正常修改：name=更新姓名1，phone=13900000001。异常修改：name=一个空格，phone=bad。
+【操作步骤】使用第二位买家的原口令码执行 PUT；再提交异常数据；最后撤销该意向并用原码查询。
+【预期结果】正常修改200，返回 name=更新姓名1、position=2；异常修改400；撤销204；原码再次查询404。
+【说明】修改不主动调整原口令码与排队顺序。</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>通过</x:v>
@@ -358,12 +366,17 @@
         <x:v>第二轮验收测试数据/R201/第1个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="44" customHeight="1">
+    <x:row r="6" ht="96" hidden="0" customHeight="1">
       <x:c r="A6" s="5" t="str">
         <x:v>R201-02</x:v>
       </x:c>
-      <x:c r="B6" s="5" t="str">
-        <x:v>手动冻结期间修改</x:v>
+      <x:c r="B6" s="11" t="str">
+        <x:v>【场景】手动冻结期间修改和撤销等待意向
+【前置数据】admin / 123456 登录；创建价格88.50元的“商品”。“队首”/13800000001排第1位，“等待买家”/13800000002排第2位，随后卖家冻结商品。
+【测试输入】正常修改：name=更新姓名2，phone=13900000002。异常修改：name=一个空格，phone=bad。
+【操作步骤】冻结接口返回200后，使用第二位买家的口令码修改；提交异常数据；再撤销并查询原码。
+【预期结果】冻结期间正常修改200，返回 name=更新姓名2、position=2；异常修改400；撤销204；原码查询404。
+【说明】手动冻结不取消等待者修改与撤销权限。</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>通过</x:v>
@@ -375,12 +388,17 @@
         <x:v>第二轮验收测试数据/R201/第2个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="44" customHeight="1">
+    <x:row r="7" ht="108" hidden="0" customHeight="1">
       <x:c r="A7" s="5" t="str">
         <x:v>R201-03</x:v>
       </x:c>
-      <x:c r="B7" s="5" t="str">
-        <x:v>他人交易期间修改</x:v>
+      <x:c r="B7" s="11" t="str">
+        <x:v>【场景】他人交易时允许等待者修改，拒绝当前交易者修改
+【前置数据】admin / 123456 登录；“队首”/13800000001先提交，“等待买家”/13800000002后提交。卖家与队首开始交易。
+【测试输入】交易者修改：name=不应修改，phone=13900000001。等待者修改：name=更新姓名3，phone=13900000003。异常值：name=一个空格，phone=bad。
+【操作步骤】分别用交易者和等待者口令码执行 PUT，再对等待者提交异常值，随后撤销等待意向并查询原码。
+【预期结果】交易者修改409；等待者修改200，返回 name=更新姓名3、position=1；异常修改400；撤销204；原码查询404。
+【说明】等待买家由第2位变第1位，原因是队首进入交易；联系信息修改本身不改变排位。</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>通过</x:v>
@@ -392,12 +410,17 @@
         <x:v>第二轮验收测试数据/R201/第3个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="44" customHeight="1">
+    <x:row r="8" ht="108" hidden="0" customHeight="1">
       <x:c r="A8" s="5" t="str">
         <x:v>R202-01</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>冻结后保留原有等待队列</x:v>
+      <x:c r="B8" s="11" t="str">
+        <x:v>【场景】冻结后保留等待排位并拒绝新意向
+【前置数据】admin / 123456 登录；主商品名称“商品”、价格88.50元；“买家”/13800000001提交成功，position=1。
+【测试输入】冻结后新增意向：name=新买家，phone=13800000002。
+【操作步骤】冻结主商品；用原口令码查询；尝试向被冻结商品提交新意向并直接下架；再解冻并开始队首交易。
+【预期结果】冻结200且 status=MANUALLY_FROZEN；原码查询200且position=1；新意向409；冻结期间下架409；解冻200且status=ON_SALE；开始交易200。
+【说明】原始脚本另有“其他商品”的隔离对照步骤，完整数据仍保留在请求与文件数据页，不另列为本轮功能成果。</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>通过</x:v>
@@ -409,12 +432,17 @@
         <x:v>第二轮验收测试数据/R202/第1个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="44" customHeight="1">
+    <x:row r="9" ht="96" hidden="0" customHeight="1">
       <x:c r="A9" s="5" t="str">
         <x:v>R202-02</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>解冻恢复交易且队列顺序不变</x:v>
+      <x:c r="B9" s="11" t="str">
+        <x:v>【场景】解冻恢复在售并允许队首开始交易
+【前置数据】admin / 123456 登录；主商品名称“商品”、价格88.50元；“买家”/13800000001先提交，position=1。
+【测试输入】冻结阶段尝试新增：name=新买家，phone=13800000002；解冻与开始交易请求均无JSON请求体。
+【操作步骤】依次执行 freeze、原码查询、被冻结商品新意向提交、unfreeze 和 trades/start。
+【预期结果】冻结200且status=MANUALLY_FROZEN；冻结后查询position=1；新意向409；解冻200且status=ON_SALE；开始交易200并返回交易意向编号。
+【说明】该实例仅有1名等待买家，验证冻结后保留第1位及解冻恢复交易，不作为多名买家完整排序验证。</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>通过</x:v>
@@ -426,12 +454,17 @@
         <x:v>第二轮验收测试数据/R202/第2个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="44" customHeight="1">
+    <x:row r="10" ht="84" hidden="0" customHeight="1">
       <x:c r="A10" s="5" t="str">
         <x:v>R202-03</x:v>
       </x:c>
-      <x:c r="B10" s="5" t="str">
-        <x:v>交易冻结不可手动解除</x:v>
+      <x:c r="B10" s="11" t="str">
+        <x:v>【场景】交易冻结不可通过手动解冻或冻结接口改变
+【前置数据】admin / 123456 登录；主商品“商品”、价格88.50元；“买家”/13800000001排第1位，卖家与其开始交易。
+【测试输入】同一商品编号依次调用 POST /unfreeze、POST /freeze；两个请求均携带卖家会话，无JSON请求体。
+【操作步骤】商品进入交易后，先尝试手动解冻，再尝试转为手动冻结。
+【预期结果】开始交易200；交易中手动解冻409；交易中转为手动冻结409。
+【说明】验证交易冻结与手动冻结的状态边界。</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>通过</x:v>
@@ -443,12 +476,17 @@
         <x:v>第二轮验收测试数据/R202/第3个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="44" customHeight="1">
+    <x:row r="11" ht="84" hidden="0" customHeight="1">
       <x:c r="A11" s="5" t="str">
         <x:v>R203-01</x:v>
       </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>原密码错误被拒绝</x:v>
+      <x:c r="B11" s="11" t="str">
+        <x:v>【场景】错误原密码被拒绝，原卖家会话仍有效
+【前置数据】使用 admin / 123456 建立 seller、other 两个卖家会话。
+【测试输入】currentPassword=wrong；newPassword=new-password-2026（17位）。
+【操作步骤】使用seller会话执行 PUT /api/seller/password；随后使用该会话 GET /api/seller/session。
+【预期结果】密码修改返回400；原seller会话查询返回200且authenticated=true。
+【说明】该实例核对的是seller会话，不将未检查的其他会话状态写成已断言。</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
         <x:v>通过</x:v>
@@ -460,12 +498,17 @@
         <x:v>第二轮验收测试数据/R203/第1个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="44" customHeight="1">
+    <x:row r="12" ht="84" hidden="0" customHeight="1">
       <x:c r="A12" s="5" t="str">
         <x:v>R203-02</x:v>
       </x:c>
-      <x:c r="B12" s="5" t="str">
-        <x:v>新密码长度限制</x:v>
+      <x:c r="B12" s="11" t="str">
+        <x:v>【场景】不足8位的新密码被拒绝，原会话仍有效
+【前置数据】使用 admin / 123456 建立 seller、other 两个卖家会话。
+【测试输入】currentPassword=123456；newPassword=short（5位，低于8位下限）。
+【操作步骤】使用seller会话提交密码修改，再查询 /api/seller/session。
+【预期结果】修改返回400；seller会话查询200且authenticated=true。
+【说明】此实例覆盖5位短密码，不据此声称已覆盖128位上限或其他全部边界。</x:v>
       </x:c>
       <x:c r="C12" s="5" t="str">
         <x:v>通过</x:v>
@@ -477,12 +520,17 @@
         <x:v>第二轮验收测试数据/R203/第2个测试实例</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="44" customHeight="1">
+    <x:row r="13" ht="108" hidden="0" customHeight="1">
       <x:c r="A13" s="5" t="str">
         <x:v>R203-03</x:v>
       </x:c>
-      <x:c r="B13" s="5" t="str">
-        <x:v>改密撤销全部旧会话</x:v>
+      <x:c r="B13" s="11" t="str">
+        <x:v>【场景】正常改密后旧密码及另一旧会话失效，新密码可登录
+【前置数据】使用 admin / 123456 建立 seller、other 两个卖家会话；测试库无商品。
+【测试输入】修改请求：currentPassword=123456，newPassword=new-password-2026。旧密码登录：admin / 123456。新密码登录：admin / new-password-2026。
+【操作步骤】seller会话改密；other旧会话查询商品；分别使用旧密码、新密码登录；新会话再次查询商品。
+【预期结果】改密204；other旧会话查询商品401；旧密码登录401；新密码登录200且authenticated=true；新会话查询200且total=0。
+【说明】上述账号密码均为独立测试库固定输入，与真实业务账号无关。</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
         <x:v>通过</x:v>
